--- a/BoM/Generic/t1-bom.xlsx
+++ b/BoM/Generic/t1-bom.xlsx
@@ -352,7 +352,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.6+1</t>
+    <t>9.0.7+1</t>
   </si>
   <si>
     <t>Component Groups:</t>

--- a/BoM/Generic/t1-bom.xlsx
+++ b/BoM/Generic/t1-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="172">
   <si>
     <t>Row</t>
   </si>
@@ -97,9 +97,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -352,7 +349,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.7+1</t>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -1093,7 +1090,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
     <col min="6" max="6" width="46.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
@@ -1111,7 +1108,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1130,13 +1127,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="C2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="3">
         <v>22</v>
@@ -1144,41 +1141,41 @@
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="C4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="C5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1186,13 +1183,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="C6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F6" s="3">
         <v>19</v>
@@ -1280,33 +1277,33 @@
         <v>25</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>18</v>
@@ -1315,10 +1312,10 @@
         <v>19</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -1333,48 +1330,48 @@
         <v>25</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>17</v>
@@ -1386,28 +1383,28 @@
         <v>25</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="M11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1415,19 +1412,19 @@
         <v>23</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>17</v>
@@ -1439,51 +1436,51 @@
         <v>25</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>24</v>
@@ -1492,48 +1489,48 @@
         <v>25</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>17</v>
@@ -1545,48 +1542,48 @@
         <v>25</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>17</v>
@@ -1598,48 +1595,48 @@
         <v>25</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="L15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="M15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>17</v>
@@ -1651,48 +1648,48 @@
         <v>25</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>17</v>
@@ -1704,48 +1701,48 @@
         <v>25</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>17</v>
@@ -1757,51 +1754,51 @@
         <v>25</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="G19" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>24</v>
@@ -1810,48 +1807,48 @@
         <v>25</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>17</v>
@@ -1863,48 +1860,48 @@
         <v>25</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>17</v>
@@ -1913,31 +1910,31 @@
         <v>24</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1958,7 +1955,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="44.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
@@ -1976,7 +1973,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1995,13 +1992,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="C2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="3">
         <v>22</v>
@@ -2009,41 +2006,41 @@
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="C4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="C5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -2051,13 +2048,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="C6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F6" s="3">
         <v>19</v>
@@ -2127,152 +2124,152 @@
         <v>19</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="K9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1">
@@ -2280,317 +2277,317 @@
         <v>23</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="K12" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="M12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K13" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="M13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>86</v>
-      </c>
       <c r="D14" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="D15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="K15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K16" s="10" t="s">
+      <c r="L16" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L16" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="M16" s="10" t="s">
+      <c r="N16" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="O16" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="P16" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="Q16" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="K17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="M17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2613,27 +2610,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
